--- a/data/projects_registry.xlsx
+++ b/data/projects_registry.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://meylon.sharepoint.com/sites/Meylon/Shared Documents/ביאן - הנהחש ולקוחות/מ.אילון אביב נכסים בעמ/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_99D59354C4111FC00472EBEE1516A2AF746AF753" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4AF4D423-9D65-409D-97CE-C5901E5D4804}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
@@ -37,9 +43,6 @@
     <t>rishon_letzion</t>
   </si>
   <si>
-    <t>ראשון לציון</t>
-  </si>
-  <si>
     <t>active</t>
   </si>
   <si>
@@ -48,16 +51,19 @@
   <si>
     <t>פרויקט תשתיות בדרום העיר</t>
   </si>
+  <si>
+    <t>נחלית עילית</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -90,13 +96,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -134,7 +148,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -168,6 +182,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -202,9 +217,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -377,11 +393,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -401,24 +417,24 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -427,8 +443,28 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="מסמך" ma:contentTypeID="0x01010054F089DE2185564F816FA57672101611" ma:contentTypeVersion="13" ma:contentTypeDescription="צור מסמך חדש." ma:contentTypeScope="" ma:versionID="f89cb87d448c193d87228dfe7299b1b7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="07697da5-2678-466b-9231-f17140fb0696" xmlns:ns3="10091922-f11e-49ea-b46f-3703d4eda96e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3b97a64ed35ab684d846dbae10ce8017" ns2:_="" ns3:_="">
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="10091922-f11e-49ea-b46f-3703d4eda96e" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="07697da5-2678-466b-9231-f17140fb0696">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010054F089DE2185564F816FA57672101611" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dfd084f78a479c3ff0473f999e65e61c">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="07697da5-2678-466b-9231-f17140fb0696" xmlns:ns3="10091922-f11e-49ea-b46f-3703d4eda96e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c6d315b3aa70d7dfa050bc071fd6676b" ns2:_="" ns3:_="">
     <xsd:import namespace="07697da5-2678-466b-9231-f17140fb0696"/>
     <xsd:import namespace="10091922-f11e-49ea-b46f-3703d4eda96e"/>
     <xsd:element name="properties">
@@ -479,7 +515,7 @@
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="תגיות תמונה" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="d6028ec3-cb3b-404c-835e-e8c107f31e42" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="d6028ec3-cb3b-404c-835e-e8c107f31e42" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -543,8 +579,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="סוג תוכן"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="כותרת"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -633,34 +669,40 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="10091922-f11e-49ea-b46f-3703d4eda96e" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="07697da5-2678-466b-9231-f17140fb0696">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{86C6F7B0-DE25-4F60-9279-4C90787AB0A3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{310C0CCA-AEA1-4526-BC91-1302930C4D59}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="10091922-f11e-49ea-b46f-3703d4eda96e"/>
+    <ds:schemaRef ds:uri="07697da5-2678-466b-9231-f17140fb0696"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7C52F1C-0FC2-4F5D-8A7B-DAE8DE98B1E7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7C52F1C-0FC2-4F5D-8A7B-DAE8DE98B1E7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{310C0CCA-AEA1-4526-BC91-1302930C4D59}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F0D58C3-047B-4C5A-882F-6F36A656E85F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="07697da5-2678-466b-9231-f17140fb0696"/>
+    <ds:schemaRef ds:uri="10091922-f11e-49ea-b46f-3703d4eda96e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/projects_registry.xlsx
+++ b/data/projects_registry.xlsx
@@ -1,76 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://meylon.sharepoint.com/sites/Meylon/Shared Documents/ביאן - הנהחש ולקוחות/מ.אילון אביב נכסים בעמ/data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_99D59354C4111FC00472EBEE1516A2AF746AF753" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4AF4D423-9D65-409D-97CE-C5901E5D4804}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" iterateDelta="1E-4"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
-  <si>
-    <t>project_id</t>
-  </si>
-  <si>
-    <t>project_name</t>
-  </si>
-  <si>
-    <t>site_name</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>start_date</t>
-  </si>
-  <si>
-    <t>notes</t>
-  </si>
-  <si>
-    <t>rishon_letzion</t>
-  </si>
-  <si>
-    <t>active</t>
-  </si>
-  <si>
-    <t>2025-01-01</t>
-  </si>
-  <si>
-    <t>פרויקט תשתיות בדרום העיר</t>
-  </si>
-  <si>
-    <t>נחלית עילית</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -89,28 +47,87 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -148,7 +165,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -182,7 +199,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -217,10 +233,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -393,78 +408,92 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>project_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>project_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>site_name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>client_name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>start_date</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>rishon_letzion</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>נחלית עילית</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>נחלית עילית</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>פרויקט תשתיות בדרום העיר</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="10091922-f11e-49ea-b46f-3703d4eda96e" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="07697da5-2678-466b-9231-f17140fb0696">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010054F089DE2185564F816FA57672101611" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dfd084f78a479c3ff0473f999e65e61c">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="07697da5-2678-466b-9231-f17140fb0696" xmlns:ns3="10091922-f11e-49ea-b46f-3703d4eda96e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c6d315b3aa70d7dfa050bc071fd6676b" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="מסמך" ma:contentTypeID="0x01010054F089DE2185564F816FA57672101611" ma:contentTypeVersion="13" ma:contentTypeDescription="צור מסמך חדש." ma:contentTypeScope="" ma:versionID="f89cb87d448c193d87228dfe7299b1b7">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="07697da5-2678-466b-9231-f17140fb0696" xmlns:ns3="10091922-f11e-49ea-b46f-3703d4eda96e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3b97a64ed35ab684d846dbae10ce8017" ns2:_="" ns3:_="">
     <xsd:import namespace="07697da5-2678-466b-9231-f17140fb0696"/>
     <xsd:import namespace="10091922-f11e-49ea-b46f-3703d4eda96e"/>
     <xsd:element name="properties">
@@ -515,7 +544,7 @@
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="d6028ec3-cb3b-404c-835e-e8c107f31e42" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="תגיות תמונה" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="d6028ec3-cb3b-404c-835e-e8c107f31e42" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -579,8 +608,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="סוג תוכן"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="כותרת"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -669,40 +698,34 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="07697da5-2678-466b-9231-f17140fb0696">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="10091922-f11e-49ea-b46f-3703d4eda96e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{310C0CCA-AEA1-4526-BC91-1302930C4D59}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="10091922-f11e-49ea-b46f-3703d4eda96e"/>
-    <ds:schemaRef ds:uri="07697da5-2678-466b-9231-f17140fb0696"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7F195BF-1B74-44F3-A8F9-B60BCC6969A2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7C52F1C-0FC2-4F5D-8A7B-DAE8DE98B1E7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3D21DEA-4C00-4202-8BB7-B61D1B1E1E09}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F0D58C3-047B-4C5A-882F-6F36A656E85F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="07697da5-2678-466b-9231-f17140fb0696"/>
-    <ds:schemaRef ds:uri="10091922-f11e-49ea-b46f-3703d4eda96e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D693B16-637D-458B-BB82-493263EDEFDA}"/>
 </file>
--- a/data/projects_registry.xlsx
+++ b/data/projects_registry.xlsx
@@ -1,34 +1,85 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
+  <si>
+    <t>project_id</t>
+  </si>
+  <si>
+    <t>project_name</t>
+  </si>
+  <si>
+    <t>site_name</t>
+  </si>
+  <si>
+    <t>client_name</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>start_date</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>rishon_letzion</t>
+  </si>
+  <si>
+    <t>rbibim</t>
+  </si>
+  <si>
+    <t>נחלית עילית</t>
+  </si>
+  <si>
+    <t>רביבים</t>
+  </si>
+  <si>
+    <t>active</t>
+  </si>
+  <si>
+    <t>2025-01-01</t>
+  </si>
+  <si>
+    <t>2024-02-01</t>
+  </si>
+  <si>
+    <t>פרויקט תשתיות בדרום העיר</t>
+  </si>
+  <si>
+    <t>נוסף בתיקון מבנה הנתונים — כרטסת מצטברת</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +98,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -408,86 +392,75 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>project_id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>project_name</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>site_name</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>client_name</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>start_date</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
+    <row r="1" spans="1:7">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>rishon_letzion</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>נחלית עילית</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>נחלית עילית</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>פרויקט תשתיות בדרום העיר</t>
-        </is>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -719,13 +692,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7F195BF-1B74-44F3-A8F9-B60BCC6969A2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89290F47-1411-40F2-8945-AC8E0C7318AF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3D21DEA-4C00-4202-8BB7-B61D1B1E1E09}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B308822E-131F-4C6A-A3B1-3DA9FA06643A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D693B16-637D-458B-BB82-493263EDEFDA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D03BFEC0-8E6F-4D08-8482-B73CEB7E8BD3}"/>
 </file>